--- a/data/trans_orig/P57C1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57C1_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha sido optimista respecto a su futuro en 2023</t>
+          <t>Población según si ha sido optimista respecto a su futuro en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19553</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20310</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>27346</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>32296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53344</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25779</t>
+          <t>25773</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56564</t>
+          <t>57915</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49486</t>
+          <t>49750</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96526</t>
+          <t>95588</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125148</t>
+          <t>125438</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>198060</t>
+          <t>197394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90215</t>
+          <t>91315</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133818</t>
+          <t>134371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227597</t>
+          <t>233291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>310054</t>
+          <t>313727</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>44,0%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171937</t>
+          <t>171535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242232</t>
+          <t>241333</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122422</t>
+          <t>122188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>168834</t>
+          <t>171575</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>312058</t>
+          <t>311032</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394909</t>
+          <t>394127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>14504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>23652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28076</t>
+          <t>27243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25336</t>
+          <t>24986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17444</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45005</t>
+          <t>44068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24917</t>
+          <t>23663</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56251</t>
+          <t>53303</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21909</t>
+          <t>22187</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54370</t>
+          <t>53632</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53910</t>
+          <t>54195</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97798</t>
+          <t>98113</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162390</t>
+          <t>159892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215536</t>
+          <t>208624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134675</t>
+          <t>128985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>253363</t>
+          <t>251621</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>302435</t>
+          <t>294827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>445650</t>
+          <t>444112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153457</t>
+          <t>156062</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207255</t>
+          <t>206460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>189546</t>
+          <t>191271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>343833</t>
+          <t>342580</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>365796</t>
+          <t>367995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>554409</t>
+          <t>552166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24704</t>
+          <t>24930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>12774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29997</t>
+          <t>30536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13383</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>28977</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29566</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52325</t>
+          <t>53104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>30627</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54872</t>
+          <t>55793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43151</t>
+          <t>43592</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>65776</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>78310</t>
+          <t>78357</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113178</t>
+          <t>113161</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>210368</t>
+          <t>213377</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>260183</t>
+          <t>259846</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>237011</t>
+          <t>237373</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>273391</t>
+          <t>274685</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>459146</t>
+          <t>461139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>522138</t>
+          <t>524696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204345</t>
+          <t>202949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252918</t>
+          <t>251059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>191813</t>
+          <t>189850</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>228904</t>
+          <t>227526</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>407606</t>
+          <t>407405</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>471037</t>
+          <t>467238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31703</t>
+          <t>32452</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43270</t>
+          <t>43597</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50715</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>30472</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49984</t>
+          <t>50786</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43334</t>
+          <t>42962</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>90706</t>
+          <t>94393</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29727</t>
+          <t>28945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>98704</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62452</t>
+          <t>61305</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>90698</t>
+          <t>90051</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>83059</t>
+          <t>79607</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>175054</t>
+          <t>174506</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>126241</t>
+          <t>139782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>439690</t>
+          <t>441783</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>331319</t>
+          <t>330091</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>411868</t>
+          <t>411235</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>388262</t>
+          <t>404396</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>806943</t>
+          <t>808436</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,57%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>285600</t>
+          <t>285286</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>705970</t>
+          <t>693763</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>192428</t>
+          <t>189753</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>247870</t>
+          <t>248670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>508159</t>
+          <t>504516</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1070281</t>
+          <t>1064679</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,6%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21732</t>
+          <t>22455</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13980</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25198</t>
+          <t>24715</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>42749</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>36508</t>
+          <t>35559</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>61553</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35952</t>
+          <t>35800</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54176</t>
+          <t>55722</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>76262</t>
+          <t>76242</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>108059</t>
+          <t>107332</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>71933</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105253</t>
+          <t>104263</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>101116</t>
+          <t>99710</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128482</t>
+          <t>128751</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>180760</t>
+          <t>180874</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>223230</t>
+          <t>224445</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>261458</t>
+          <t>259326</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>304961</t>
+          <t>306116</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>233154</t>
+          <t>232903</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>267034</t>
+          <t>268747</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>504063</t>
+          <t>503765</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>561378</t>
+          <t>562760</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>111067</t>
+          <t>110771</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>148689</t>
+          <t>149974</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>104146</t>
+          <t>103826</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>132894</t>
+          <t>133945</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>224028</t>
+          <t>223156</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>271185</t>
+          <t>273331</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18550</t>
+          <t>18134</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>24552</t>
+          <t>25641</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18136</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>32034</t>
+          <t>32540</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>57871</t>
+          <t>58345</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>31319</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>81698</t>
+          <t>81371</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>56075</t>
+          <t>57452</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>79046</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>33979</t>
+          <t>32447</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>127374</t>
+          <t>125922</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>70821</t>
+          <t>81559</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>194938</t>
+          <t>195047</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>164593</t>
+          <t>164257</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>194970</t>
+          <t>195954</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>261269</t>
+          <t>261076</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>512317</t>
+          <t>516542</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>444904</t>
+          <t>444504</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>783057</t>
+          <t>758770</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>74812</t>
+          <t>74288</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>101672</t>
+          <t>99922</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>40701</t>
+          <t>39995</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>155133</t>
+          <t>155180</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>85761</t>
+          <t>86629</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>242125</t>
+          <t>240444</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>20181</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33006</t>
+          <t>32061</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>27426</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>43049</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>19791</t>
+          <t>19962</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>34244</t>
+          <t>34577</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>53016</t>
+          <t>52392</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>72410</t>
+          <t>71677</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>75657</t>
+          <t>77064</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>102004</t>
+          <t>101292</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>63283</t>
+          <t>64538</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>87435</t>
+          <t>89085</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>105630</t>
+          <t>106739</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>130966</t>
+          <t>132419</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>178708</t>
+          <t>177442</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>213735</t>
+          <t>211865</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>104993</t>
+          <t>105528</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>130795</t>
+          <t>130741</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>144140</t>
+          <t>143663</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>171758</t>
+          <t>171479</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>257339</t>
+          <t>255821</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>296553</t>
+          <t>296041</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,19%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>41569</t>
+          <t>43215</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>62602</t>
+          <t>64104</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>47469</t>
+          <t>47305</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>67608</t>
+          <t>67480</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>93944</t>
+          <t>95554</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>123474</t>
+          <t>124949</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>49309</t>
+          <t>48274</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>82600</t>
+          <t>83137</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>63813</t>
+          <t>65137</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>99862</t>
+          <t>101700</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>124891</t>
+          <t>124827</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>175927</t>
+          <t>179840</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>126441</t>
+          <t>126789</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>193993</t>
+          <t>192566</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>181360</t>
+          <t>183988</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>254479</t>
+          <t>257403</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>332625</t>
+          <t>338427</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>432127</t>
+          <t>435654</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>316511</t>
+          <t>311671</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>454903</t>
+          <t>452641</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>421735</t>
+          <t>414207</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>571656</t>
+          <t>572000</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>796888</t>
+          <t>816696</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>999056</t>
+          <t>1004693</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1160894</t>
+          <t>1150978</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1611729</t>
+          <t>1609754</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1576924</t>
+          <t>1583768</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2104043</t>
+          <t>2136869</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2882394</t>
+          <t>2898143</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3524172</t>
+          <t>3529577</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1166794</t>
+          <t>1164569</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1807822</t>
+          <t>1794774</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>911991</t>
+          <t>925272</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1240325</t>
+          <t>1232117</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2183899</t>
+          <t>2188436</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2959149</t>
+          <t>2952345</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57C1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57C1_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,77 +750,77 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5836</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19715</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>7489</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1675</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>23987</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5448</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17863</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>5612</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>19829</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9705</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27346</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>26559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16694</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52573</t>
+          <t>49534</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39857</t>
+          <t>43538</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25773</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57915</t>
+          <t>62246</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>70680</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49750</t>
+          <t>53814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>95588</t>
+          <t>100703</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>143418</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125438</t>
+          <t>113386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>197394</t>
+          <t>178359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>111539</t>
+          <t>135329</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91315</t>
+          <t>110745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>134371</t>
+          <t>161713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>271000</t>
+          <t>278748</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>233291</t>
+          <t>235424</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>313727</t>
+          <t>319376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>208000</t>
+          <t>230717</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171535</t>
+          <t>196086</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>241333</t>
+          <t>261220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>146556</t>
+          <t>164600</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122188</t>
+          <t>139712</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171575</t>
+          <t>189727</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>354556</t>
+          <t>395318</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>311032</t>
+          <t>352095</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394127</t>
+          <t>437692</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>313038</t>
+          <t>360797</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313038</t>
+          <t>360797</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313038</t>
+          <t>360797</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>713025</t>
+          <t>768591</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>713025</t>
+          <t>768591</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>713025</t>
+          <t>768591</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>13281</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27243</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>15966</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24986</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44068</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>38871</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53303</t>
+          <t>54882</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>47358</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22187</t>
+          <t>35100</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53632</t>
+          <t>62653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>74874</t>
+          <t>86228</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>54195</t>
+          <t>65878</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>98113</t>
+          <t>106572</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>185707</t>
+          <t>211741</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159892</t>
+          <t>183465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208624</t>
+          <t>241665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>211717</t>
+          <t>235913</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>128985</t>
+          <t>213476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>251621</t>
+          <t>259419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>397425</t>
+          <t>447654</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>294827</t>
+          <t>411804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>444112</t>
+          <t>483496</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>180417</t>
+          <t>206389</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156062</t>
+          <t>177442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206460</t>
+          <t>236375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>240053</t>
+          <t>195292</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>191271</t>
+          <t>171508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>342580</t>
+          <t>217277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>420470</t>
+          <t>401681</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>367995</t>
+          <t>366801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>552166</t>
+          <t>437295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>24522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24930</t>
+          <t>28612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>22372</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>32580</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,27 +2237,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>16006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>33182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>40562</t>
+          <t>45388</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30566</t>
+          <t>34323</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53104</t>
+          <t>58836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>41523</t>
+          <t>53281</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>40203</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55793</t>
+          <t>70649</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53296</t>
+          <t>61382</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43592</t>
+          <t>49278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65776</t>
+          <t>74951</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>94819</t>
+          <t>114663</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>78357</t>
+          <t>95071</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113161</t>
+          <t>133420</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>235480</t>
+          <t>264757</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>213377</t>
+          <t>236623</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>259846</t>
+          <t>290503</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>255778</t>
+          <t>294957</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>237373</t>
+          <t>274974</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>274685</t>
+          <t>316191</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>491257</t>
+          <t>559713</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>461139</t>
+          <t>529888</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>524696</t>
+          <t>594293</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>228247</t>
+          <t>267392</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202949</t>
+          <t>240220</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251059</t>
+          <t>296725</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>208636</t>
+          <t>237335</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>189850</t>
+          <t>216524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227526</t>
+          <t>257618</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>436883</t>
+          <t>504727</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>407405</t>
+          <t>471498</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>467238</t>
+          <t>539057</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>541659</t>
+          <t>620729</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>541659</t>
+          <t>620729</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>541659</t>
+          <t>620729</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1077997</t>
+          <t>1241566</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1077997</t>
+          <t>1241566</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1077997</t>
+          <t>1241566</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>31684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>30845</t>
+          <t>33905</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>24912</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43597</t>
+          <t>50238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31901</t>
+          <t>33571</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>22909</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50957</t>
+          <t>45806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>39877</t>
+          <t>43590</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>34499</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50786</t>
+          <t>55285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>71778</t>
+          <t>77161</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42962</t>
+          <t>62837</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94393</t>
+          <t>94850</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>65141</t>
+          <t>73404</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28945</t>
+          <t>57910</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>98704</t>
+          <t>90317</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>76017</t>
+          <t>83254</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61305</t>
+          <t>70048</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>90051</t>
+          <t>97373</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>141158</t>
+          <t>156659</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>79607</t>
+          <t>135279</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>174506</t>
+          <t>180950</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>310588</t>
+          <t>339586</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139782</t>
+          <t>313134</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>441783</t>
+          <t>368247</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>357805</t>
+          <t>350422</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>330091</t>
+          <t>330574</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>411235</t>
+          <t>372232</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>668393</t>
+          <t>690009</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>404396</t>
+          <t>653931</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>808436</t>
+          <t>725696</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>460751</t>
+          <t>233712</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>285286</t>
+          <t>205917</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>693763</t>
+          <t>260160</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>225633</t>
+          <t>244028</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>189753</t>
+          <t>224154</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>248670</t>
+          <t>266561</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>686383</t>
+          <t>477740</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>504516</t>
+          <t>449387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1064679</t>
+          <t>512398</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>711775</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>711775</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>711775</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1598557</t>
+          <t>1435474</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1598557</t>
+          <t>1435474</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1598557</t>
+          <t>1435474</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13258</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26594</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>33253</t>
+          <t>36994</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24715</t>
+          <t>27889</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>42749</t>
+          <t>48775</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>46556</t>
+          <t>50256</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35559</t>
+          <t>38257</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>63302</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>44326</t>
+          <t>49403</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>40316</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55722</t>
+          <t>61453</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>90882</t>
+          <t>99660</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>76242</t>
+          <t>81780</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>107332</t>
+          <t>116725</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>87015</t>
+          <t>92426</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71933</t>
+          <t>76388</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>104263</t>
+          <t>109311</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>114347</t>
+          <t>126411</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>99710</t>
+          <t>111589</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128751</t>
+          <t>140987</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>201362</t>
+          <t>218837</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>180874</t>
+          <t>196591</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>224445</t>
+          <t>242555</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282935</t>
+          <t>306848</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>259326</t>
+          <t>282978</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>306116</t>
+          <t>330752</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>249583</t>
+          <t>274337</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>232903</t>
+          <t>253626</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>268747</t>
+          <t>294190</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>532518</t>
+          <t>581185</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>503765</t>
+          <t>551859</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>562760</t>
+          <t>610323</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,26%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>129682</t>
+          <t>143156</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>110771</t>
+          <t>122227</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>149974</t>
+          <t>163301</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>117787</t>
+          <t>134613</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>103826</t>
+          <t>119031</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>133945</t>
+          <t>153540</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>247469</t>
+          <t>277769</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>223156</t>
+          <t>253966</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>273331</t>
+          <t>305375</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>545247</t>
+          <t>606086</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>545247</t>
+          <t>606086</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>545247</t>
+          <t>606086</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1105484</t>
+          <t>1214445</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1105484</t>
+          <t>1214445</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1105484</t>
+          <t>1214445</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18134</t>
+          <t>17022</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>24471</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>19138</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>32540</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>35458</t>
+          <t>39548</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>31301</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>49108</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>59929</t>
+          <t>65434</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>31319</t>
+          <t>54692</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>81371</t>
+          <t>77925</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>67408</t>
+          <t>72040</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>57452</t>
+          <t>60421</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>85207</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>80295</t>
+          <t>88089</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>76497</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>125922</t>
+          <t>100798</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>147703</t>
+          <t>160128</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>81559</t>
+          <t>143813</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>195047</t>
+          <t>178274</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>180455</t>
+          <t>201739</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>164257</t>
+          <t>185932</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>195954</t>
+          <t>219753</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>382373</t>
+          <t>191388</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>261076</t>
+          <t>177433</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>516542</t>
+          <t>206836</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>562828</t>
+          <t>393126</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>444504</t>
+          <t>371421</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>758770</t>
+          <t>416135</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>87304</t>
+          <t>98522</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>74288</t>
+          <t>82947</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>99922</t>
+          <t>112865</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>98689</t>
+          <t>107797</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>39995</t>
+          <t>95005</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>155180</t>
+          <t>120476</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>185993</t>
+          <t>206318</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>86629</t>
+          <t>186481</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>240444</t>
+          <t>225923</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>366029</t>
+          <t>404798</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>366029</t>
+          <t>404798</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>366029</t>
+          <t>404798</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>607300</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>607300</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>607300</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>973329</t>
+          <t>842807</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>973329</t>
+          <t>842807</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>973329</t>
+          <t>842807</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13633</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>26596</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>19816</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>32061</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>35824</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>28766</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>43049</t>
+          <t>44675</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>26328</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>20706</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>36382</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>61890</t>
+          <t>68891</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>52392</t>
+          <t>59095</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>71677</t>
+          <t>81427</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>88217</t>
+          <t>96678</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>77064</t>
+          <t>83356</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>101292</t>
+          <t>111769</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>75761</t>
+          <t>81904</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>64538</t>
+          <t>69613</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>89085</t>
+          <t>95472</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>118279</t>
+          <t>127945</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>106739</t>
+          <t>113910</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>132419</t>
+          <t>141634</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>194040</t>
+          <t>209849</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>177442</t>
+          <t>190076</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>211865</t>
+          <t>228997</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>118108</t>
+          <t>129196</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>105528</t>
+          <t>114665</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>130741</t>
+          <t>144708</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>157366</t>
+          <t>171598</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>143663</t>
+          <t>156202</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>171479</t>
+          <t>186602</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>275474</t>
+          <t>300794</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>255821</t>
+          <t>279760</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>296041</t>
+          <t>321512</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>52393</t>
+          <t>60879</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>43215</t>
+          <t>49547</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>64104</t>
+          <t>75121</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>56906</t>
+          <t>63603</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>47305</t>
+          <t>53113</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>67480</t>
+          <t>75206</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>109299</t>
+          <t>124482</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>95554</t>
+          <t>107965</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>124949</t>
+          <t>143070</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>281599</t>
+          <t>308993</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>281599</t>
+          <t>308993</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>281599</t>
+          <t>308993</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>420139</t>
+          <t>458634</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>420139</t>
+          <t>458634</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>420139</t>
+          <t>458634</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>701737</t>
+          <t>767628</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>701737</t>
+          <t>767628</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>701737</t>
+          <t>767628</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>65273</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>56664</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>83137</t>
+          <t>91123</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>83569</t>
+          <t>90032</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>65137</t>
+          <t>75545</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>101700</t>
+          <t>108369</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>148842</t>
+          <t>162368</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>124827</t>
+          <t>142048</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>179840</t>
+          <t>188852</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>165270</t>
+          <t>174453</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>126789</t>
+          <t>151211</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>192566</t>
+          <t>198556</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>226484</t>
+          <t>251908</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>183988</t>
+          <t>227786</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>257403</t>
+          <t>278136</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>391753</t>
+          <t>426361</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>338427</t>
+          <t>389884</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>435654</t>
+          <t>460634</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>404447</t>
+          <t>442512</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>311671</t>
+          <t>406330</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>452641</t>
+          <t>484479</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>520189</t>
+          <t>577978</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>414207</t>
+          <t>540352</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>572000</t>
+          <t>619720</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>924636</t>
+          <t>1020490</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>816696</t>
+          <t>967213</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1004693</t>
+          <t>1081329</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1472734</t>
+          <t>1597285</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1150978</t>
+          <t>1537246</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1609754</t>
+          <t>1665747</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1726162</t>
+          <t>1653945</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1583768</t>
+          <t>1603071</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2136869</t>
+          <t>1708570</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>3198895</t>
+          <t>3251230</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2898143</t>
+          <t>3173730</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3529577</t>
+          <t>3337507</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>46,04%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1346795</t>
+          <t>1240767</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1164569</t>
+          <t>1181856</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1794774</t>
+          <t>1302138</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1094259</t>
+          <t>1147268</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>925272</t>
+          <t>1096127</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1232117</t>
+          <t>1203147</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>2441053</t>
+          <t>2388036</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2188436</t>
+          <t>2300544</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2952345</t>
+          <t>2471910</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3454518</t>
+          <t>3527354</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3454518</t>
+          <t>3527354</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3454518</t>
+          <t>3527354</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3721130</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3721130</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3721130</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7105180</t>
+          <t>7248484</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7105180</t>
+          <t>7248484</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7105180</t>
+          <t>7248484</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
